--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1307,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3541-2-CM25</t>
+          <t>2412-138-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1376,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.935.200-9</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,20 +1399,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9517.98</v>
+        <v>846.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2412-138-CM25</t>
+          <t>3541-2-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1441,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.935.200-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,14 +1464,18 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>846.04</v>
+        <v>9517.98</v>
       </c>
     </row>
     <row r="17">
@@ -1477,7 +1529,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1917,7 +2001,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1195-72-CM25</t>
+          <t>633-141-SE25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +2016,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,43 +2026,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24276</v>
+        <v>544960.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4052-24-CM25</t>
+          <t>1195-72-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,97 +2091,170 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9236.299999999999</v>
+        <v>24276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>4052-24-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.251.200-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>9236.299999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>770-34-CM25</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>feb-2025</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>60.604.000-8</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>77.622.841-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>19163.76</v>
       </c>
     </row>
